--- a/data/user_log/food.xlsx
+++ b/data/user_log/food.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="User History" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1633,4 +1634,112 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A19:J19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>25</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>50</v>
+      </c>
+      <c r="F19" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Normal weight - Maintain a balanced diet and exercise.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Non-veg</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>['zinc', 'iron']</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+Non-veg
+Fish
+  - Mollusks, oyster, eastern, farmed, raw (zinc: 37.9, iron: 5.78)
+  - Mollusks, oyster, eastern, wild, raw (zinc: 39.3, iron: 4.61)
+  - Mollusks, oyster, Pacific, raw (zinc: 16.6, iron: 5.11)
+  - Crustaceans, spiny lobster, mixed species, raw (zinc: 5.67, iron: 1.22)
+Lamb
+  - Lamb, variety meats and by-products, spleen, raw (zinc: 2.84, iron: 41.9)
+  - Lamb, variety meats and by-products, mechanically separated, raw (zinc: 3.72, iron: 5.9)
+  - Game meat, bison, shoulder clod, separable lean only, trimmed to 0" fat, raw (zinc: 5.0, iron: 3.0)
+  - Lamb, variety meats and by-products, lungs, raw (zinc: 1.8, iron: 6.4)
+  - Game meat, elk, ground, raw (zinc: 5.4, iron: 2.75)
+  - Game meat, goat, raw (zinc: 4.0, iron: 2.83)
+  - Game meat, beaver, raw (zinc: 0.0, iron: 6.9)
+  - Lamb, foreshank, separable lean and fat, trimmed to 1/4" fat, choice, raw (zinc: 5.22, iron: 1.67)
+  - Game meat, bison, top sirloin, separable lean only, trimmed to 0" fat, raw (zinc: 3.4, iron: 3.0)
+  - Game meat, elk, raw (zinc: 2.4, iron: 2.76)
+  - Game meat, bison, ribeye, separable lean only, trimmed to 0" fat, raw (zinc: 3.2, iron: 2.8)
+  - Game meat, moose, raw (zinc: 2.8, iron: 3.21)
+  - Game meat, bison, separable lean only, raw (zinc: 2.8, iron: 2.6)
+  - Game meat, bear, raw (zinc: 0.0, iron: 6.65)
+  - Veal, variety meats and by-products, spleen, raw (zinc: 1.61, iron: 9.32)
+Pork
+  - Pork, fresh, variety meats and by-products, spleen, raw (zinc: 2.54, iron: 22.3)
+  - Pork, fresh, variety meats and by-products, lungs, raw (zinc: 2.03, iron: 18.9)
+Chicken
+  - Chicken, heart, all classes, raw (zinc: 6.59, iron: 5.96)
+Beef
+  - Beef, chuck, short ribs, boneless, separable lean and fat, trimmed to 0" fat, all grades, raw (zinc: 7.07, iron: 2.24)
+  - Beef, chuck, roast, boneless, choice, raw (zinc: 5.39, iron: 2.06)
+  - Beef, chuck, mock tender steak, boneless, separable lean and fat, trimmed to 0" fat, all grades, raw (zinc: 7.93, iron: 2.43)
+  - Beef, flank, steak, boneless, choice, raw (zinc: 5.56, iron: 1.83)
+  - Beef, loin, top sirloin cap steak, boneless, separable lean and fat, trimmed to 1/8" fat, all grades, raw (zinc: 7.12, iron: 2.41)
+  - Beef, chuck eye roast, boneless, America's Beef Roast, separable lean and fat, trimmed to 0" fat, all grades, raw (zinc: 7.52, iron: 2.08)
+  - Beef, chuck eye steak, boneless, separable lean and fat, trimmed to 0" fat, all grades, raw (zinc: 7.26, iron: 2.1)
+  - Beef, chuck eye Country-Style ribs, boneless, separable lean and fat, trimmed to 0" fat, all grades, raw (zinc: 6.65, iron: 2.1)
+  - Beef, chuck, shoulder clod, top blade, steak, separable lean and fat, trimmed to 0" fat, all grades, raw (zinc: 6.88, iron: 2.36)
+  - Beef, chuck, under blade pot roast or steak, boneless, separable lean and fat, trimmed to 0" fat, all grades, raw (zinc: 6.99, iron: 2.19)
+  - Beef, ribeye, steak, boneless, choice, raw (zinc: 4.06, iron: 1.64)
+  - Beef, chuck, blade roast, separable lean and fat, trimmed to 1/8" fat, all grades, raw (zinc: 4.98, iron: 2.04)
+  - Beef, plate steak, boneless, inside skirt, separable lean and fat, trimmed to 0" fat, all grades, raw (zinc: 5.99, iron: 1.71)
+  - Beef, chuck, clod roast, separable lean only, trimmed to 1/4" fat, all grades, raw (zinc: 4.83, iron: 2.35)
+Veg
+Vegetable
+  - Mushrooms, morel, raw (zinc: 2.03, iron: 12.2)
+  - Lemon grass (citronella), raw (zinc: 2.23, iron: 8.17)
+  - Seaweed, irishmoss, raw (zinc: 1.95, iron: 8.9)
+Legumes
+  - Tofu, raw, regular, prepared with calcium sulfate (zinc: 0.8, iron: 5.36)
+</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/user_log/food.xlsx
+++ b/data/user_log/food.xlsx
@@ -1675,66 +1675,54 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Non-veg</t>
+          <t>Veg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['zinc', 'iron']</t>
+          <t>['calcium', 'Niacin', 'folate_total']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
           <t xml:space="preserve">
-Non-veg
-Fish
-  - Mollusks, oyster, eastern, farmed, raw (zinc: 37.9, iron: 5.78)
-  - Mollusks, oyster, eastern, wild, raw (zinc: 39.3, iron: 4.61)
-  - Mollusks, oyster, Pacific, raw (zinc: 16.6, iron: 5.11)
-  - Crustaceans, spiny lobster, mixed species, raw (zinc: 5.67, iron: 1.22)
-Lamb
-  - Lamb, variety meats and by-products, spleen, raw (zinc: 2.84, iron: 41.9)
-  - Lamb, variety meats and by-products, mechanically separated, raw (zinc: 3.72, iron: 5.9)
-  - Game meat, bison, shoulder clod, separable lean only, trimmed to 0" fat, raw (zinc: 5.0, iron: 3.0)
-  - Lamb, variety meats and by-products, lungs, raw (zinc: 1.8, iron: 6.4)
-  - Game meat, elk, ground, raw (zinc: 5.4, iron: 2.75)
-  - Game meat, goat, raw (zinc: 4.0, iron: 2.83)
-  - Game meat, beaver, raw (zinc: 0.0, iron: 6.9)
-  - Lamb, foreshank, separable lean and fat, trimmed to 1/4" fat, choice, raw (zinc: 5.22, iron: 1.67)
-  - Game meat, bison, top sirloin, separable lean only, trimmed to 0" fat, raw (zinc: 3.4, iron: 3.0)
-  - Game meat, elk, raw (zinc: 2.4, iron: 2.76)
-  - Game meat, bison, ribeye, separable lean only, trimmed to 0" fat, raw (zinc: 3.2, iron: 2.8)
-  - Game meat, moose, raw (zinc: 2.8, iron: 3.21)
-  - Game meat, bison, separable lean only, raw (zinc: 2.8, iron: 2.6)
-  - Game meat, bear, raw (zinc: 0.0, iron: 6.65)
-  - Veal, variety meats and by-products, spleen, raw (zinc: 1.61, iron: 9.32)
-Pork
-  - Pork, fresh, variety meats and by-products, spleen, raw (zinc: 2.54, iron: 22.3)
-  - Pork, fresh, variety meats and by-products, lungs, raw (zinc: 2.03, iron: 18.9)
-Chicken
-  - Chicken, heart, all classes, raw (zinc: 6.59, iron: 5.96)
-Beef
-  - Beef, chuck, short ribs, boneless, separable lean and fat, trimmed to 0" fat, all grades, raw (zinc: 7.07, iron: 2.24)
-  - Beef, chuck, roast, boneless, choice, raw (zinc: 5.39, iron: 2.06)
-  - Beef, chuck, mock tender steak, boneless, separable lean and fat, trimmed to 0" fat, all grades, raw (zinc: 7.93, iron: 2.43)
-  - Beef, flank, steak, boneless, choice, raw (zinc: 5.56, iron: 1.83)
-  - Beef, loin, top sirloin cap steak, boneless, separable lean and fat, trimmed to 1/8" fat, all grades, raw (zinc: 7.12, iron: 2.41)
-  - Beef, chuck eye roast, boneless, America's Beef Roast, separable lean and fat, trimmed to 0" fat, all grades, raw (zinc: 7.52, iron: 2.08)
-  - Beef, chuck eye steak, boneless, separable lean and fat, trimmed to 0" fat, all grades, raw (zinc: 7.26, iron: 2.1)
-  - Beef, chuck eye Country-Style ribs, boneless, separable lean and fat, trimmed to 0" fat, all grades, raw (zinc: 6.65, iron: 2.1)
-  - Beef, chuck, shoulder clod, top blade, steak, separable lean and fat, trimmed to 0" fat, all grades, raw (zinc: 6.88, iron: 2.36)
-  - Beef, chuck, under blade pot roast or steak, boneless, separable lean and fat, trimmed to 0" fat, all grades, raw (zinc: 6.99, iron: 2.19)
-  - Beef, ribeye, steak, boneless, choice, raw (zinc: 4.06, iron: 1.64)
-  - Beef, chuck, blade roast, separable lean and fat, trimmed to 1/8" fat, all grades, raw (zinc: 4.98, iron: 2.04)
-  - Beef, plate steak, boneless, inside skirt, separable lean and fat, trimmed to 0" fat, all grades, raw (zinc: 5.99, iron: 1.71)
-  - Beef, chuck, clod roast, separable lean only, trimmed to 1/4" fat, all grades, raw (zinc: 4.83, iron: 2.35)
 Veg
+Legumes
+  - Peanuts, spanish, raw (calcium: 106.0, Niacin: 15.9, folate_total: 0.24)
+  - Peanuts, valencia, raw (calcium: 62.0, Niacin: 12.9, folate_total: 0.246)
+  - Beans, adzuki, mature seeds, raw (calcium: 66.0, Niacin: 2.63, folate_total: 0.622)
+  - Chickpeas (garbanzo beans, bengal gram), mature seeds, raw (calcium: 57.0, Niacin: 1.54, folate_total: 0.557)
+  - Tofu, raw, firm, prepared with calcium sulfate (calcium: 683.0, Niacin: 0.381, folate_total: 0.029)
+  - Mung beans, mature seeds, raw (calcium: 132.0, Niacin: 2.25, folate_total: 0.625)
+  - Beans, french, mature seeds, raw (calcium: 186.0, Niacin: 2.08, folate_total: 0.399)
+  - Beans, kidney, royal red, mature seeds, raw (calcium: 131.0, Niacin: 2.11, folate_total: 0.393)
+  - Pigeon peas (red gram), mature seeds, raw (calcium: 130.0, Niacin: 2.96, folate_total: 0.456)
+  - Beans, kidney, california red, mature seeds, raw (calcium: 195.0, Niacin: 2.06, folate_total: 0.394)
+  - Beans, cranberry (roman), mature seeds, raw (calcium: 127.0, Niacin: 1.46, folate_total: 0.604)
+  - Beans, kidney, all types, mature seeds, raw (calcium: 143.0, Niacin: 2.06, folate_total: 0.394)
 Vegetable
-  - Mushrooms, morel, raw (zinc: 2.03, iron: 12.2)
-  - Lemon grass (citronella), raw (zinc: 2.23, iron: 8.17)
-  - Seaweed, irishmoss, raw (zinc: 1.95, iron: 8.9)
-Legumes
-  - Tofu, raw, regular, prepared with calcium sulfate (zinc: 0.8, iron: 5.36)
+  - Fireweed, leaves, raw (calcium: 429.0, Niacin: 4.67, folate_total: 0.112)
+  - Arrowroot, raw (calcium: 6.0, Niacin: 1.69, folate_total: 0.338)
+  - Epazote, raw (calcium: 275.0, Niacin: 0.639, folate_total: 0.215)
+  - Mustard spinach, (tendergreen), raw (calcium: 210.0, Niacin: 0.678, folate_total: 0.159)
+  - Cowpeas (blackeyes), immature seeds, raw (calcium: 126.0, Niacin: 1.45, folate_total: 0.168)
+  - Seaweed, wakame, raw (calcium: 150.0, Niacin: 1.6, folate_total: 0.196)
+  - Grape leaves, raw (calcium: 363.0, Niacin: 2.36, folate_total: 0.083)
+  - Arugula, baby, raw (calcium: 204.0, Niacin: 0.0, folate_total: 0.149)
+  - Seaweed, kelp, raw (calcium: 168.0, Niacin: 0.47, folate_total: 0.18)
+  - Soybeans, green, raw (calcium: 197.0, Niacin: 1.65, folate_total: 0.165)
+Cheese
+  - Cheese, American, nonfat or fat free (calcium: 789.0, Niacin: 5.56, folate_total: 0.009)
+  - Cheese, Mexican, blend, reduced fat (calcium: 1150.0, Niacin: 0.06, folate_total: 0.02)
+  - Cheese, cheddar, nonfat or fat free (calcium: 893.0, Niacin: 0.051, folate_total: 0.011)
+  - Cheese, monterey (calcium: 746.0, Niacin: 0.093, folate_total: 0.018)
+  - Cheese, port de salut (calcium: 650.0, Niacin: 0.06, folate_total: 0.018)
+  - Cheese, mozzarella, part skim milk (calcium: 782.0, Niacin: 0.105, folate_total: 0.009)
+  - Cheese, swiss, low fat (calcium: 961.0, Niacin: 0.09, folate_total: 0.006)
+  - Cheese, swiss, low sodium (calcium: 961.0, Niacin: 0.09, folate_total: 0.006)
+Grain
+  - Rice, white, medium-grain, raw, enriched (calcium: 9.0, Niacin: 5.09, folate_total: 0.231)
+  - Rice, white, long-grain, regular, raw, enriched (calcium: 28.0, Niacin: 4.19, folate_total: 0.231)
 </t>
         </is>
       </c>
